--- a/assets/demo/TongTai-Commerce-Demo-100-Products.xlsx
+++ b/assets/demo/TongTai-Commerce-Demo-100-Products.xlsx
@@ -19831,7 +19831,7 @@
         <v>200</v>
       </c>
       <c r="H67" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I67" t="n">
         <v>4.6</v>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Rẻ hơn nhưng giao chậm hơn</t>
+          <t>Rẻ hơn và giao nhanh hơn</t>
         </is>
       </c>
     </row>
@@ -20303,7 +20303,7 @@
         <v>24</v>
       </c>
       <c r="H76" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>4.4</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Rẻ hơn nhưng giao chậm hơn</t>
+          <t>Rẻ hơn và giao nhanh hơn</t>
         </is>
       </c>
     </row>
@@ -20773,7 +20773,7 @@
         <v>2</v>
       </c>
       <c r="H85" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I85" t="n">
         <v>4.3</v>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Rẻ hơn nhưng giao chậm hơn</t>
+          <t>Rẻ hơn và giao nhanh hơn</t>
         </is>
       </c>
     </row>
@@ -21245,7 +21245,7 @@
         <v>20</v>
       </c>
       <c r="H94" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
         <v>4.5</v>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Rẻ hơn nhưng giao chậm hơn</t>
+          <t>Rẻ hơn và giao nhanh hơn</t>
         </is>
       </c>
     </row>
